--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$44</f>
+              <f>'DailyProfit'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$44</f>
+              <f>'DailyProfit'!$B$2:$B$45</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$44</f>
+              <f>'DailyProfit'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$44</f>
+              <f>'DailyProfit'!$D$2:$D$45</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$44</f>
+              <f>'DailyProfit'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$44</f>
+              <f>'DailyProfit'!$F$2:$F$45</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$44</f>
+              <f>'DailyProfit'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$44</f>
+              <f>'DailyProfit'!$G$2:$G$45</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$44</f>
+              <f>'DailyProfit'!$A$2:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$44</f>
+              <f>'DailyProfit'!$H$2:$H$45</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2656,7 +2656,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
@@ -2687,6 +2687,40 @@
       </c>
       <c r="J44" s="11" t="n">
         <v>110609</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n">
+        <v>106931</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>565278</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>16429681</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>0.0009993551401869158</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.005282971962616822</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>0.1535484205607477</v>
+      </c>
+      <c r="I45" s="11" t="n">
+        <v>-3678</v>
+      </c>
+      <c r="J45" s="11" t="n">
+        <v>106931</v>
       </c>
     </row>
   </sheetData>
@@ -2764,7 +2798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -2785,7 +2819,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>110609</v>
+        <v>106931</v>
       </c>
     </row>
     <row r="5">
@@ -2795,7 +2829,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>458347</v>
+        <v>565278</v>
       </c>
     </row>
     <row r="6">
@@ -2805,7 +2839,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16322750</v>
+        <v>16429681</v>
       </c>
     </row>
     <row r="7">
@@ -2815,7 +2849,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001033728971962617</v>
+        <v>0.0009993551401869158</v>
       </c>
     </row>
     <row r="8">
@@ -2825,7 +2859,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.004283616822429907</v>
+        <v>0.005282971962616822</v>
       </c>
     </row>
     <row r="9">
@@ -2835,7 +2869,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1525490654205607</v>
+        <v>0.1535484205607477</v>
       </c>
     </row>
     <row r="10">
@@ -2845,7 +2879,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3363262.930232558</v>
+        <v>3289255.386363636</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$45</f>
+              <f>'DailyProfit'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$45</f>
+              <f>'DailyProfit'!$B$2:$B$46</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$45</f>
+              <f>'DailyProfit'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$45</f>
+              <f>'DailyProfit'!$D$2:$D$46</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$45</f>
+              <f>'DailyProfit'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$45</f>
+              <f>'DailyProfit'!$F$2:$F$46</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$45</f>
+              <f>'DailyProfit'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$45</f>
+              <f>'DailyProfit'!$G$2:$G$46</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$45</f>
+              <f>'DailyProfit'!$A$2:$A$46</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$45</f>
+              <f>'DailyProfit'!$H$2:$H$46</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2690,7 +2690,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
@@ -2721,6 +2721,40 @@
       </c>
       <c r="J45" s="11" t="n">
         <v>106931</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>152726</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>718004</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>16582407</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>0.001427345794392523</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.006710317757009346</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>0.1549757663551402</v>
+      </c>
+      <c r="I46" s="11" t="n">
+        <v>45795</v>
+      </c>
+      <c r="J46" s="11" t="n">
+        <v>152726</v>
       </c>
     </row>
   </sheetData>
@@ -2798,7 +2832,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2853,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>106931</v>
+        <v>152726</v>
       </c>
     </row>
     <row r="5">
@@ -2829,7 +2863,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>565278</v>
+        <v>718004</v>
       </c>
     </row>
     <row r="6">
@@ -2839,7 +2873,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16429681</v>
+        <v>16582407</v>
       </c>
     </row>
     <row r="7">
@@ -2849,7 +2883,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0009993551401869158</v>
+        <v>0.001427345794392523</v>
       </c>
     </row>
     <row r="8">
@@ -2859,7 +2893,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.005282971962616822</v>
+        <v>0.006710317757009346</v>
       </c>
     </row>
     <row r="9">
@@ -2869,7 +2903,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1535484205607477</v>
+        <v>0.1549757663551402</v>
       </c>
     </row>
     <row r="10">
@@ -2879,7 +2913,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3289255.386363636</v>
+        <v>3219554.733333333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$46</f>
+              <f>'DailyProfit'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$46</f>
+              <f>'DailyProfit'!$B$2:$B$47</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$46</f>
+              <f>'DailyProfit'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$46</f>
+              <f>'DailyProfit'!$D$2:$D$47</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$46</f>
+              <f>'DailyProfit'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$46</f>
+              <f>'DailyProfit'!$F$2:$F$47</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$46</f>
+              <f>'DailyProfit'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$46</f>
+              <f>'DailyProfit'!$G$2:$G$47</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$46</f>
+              <f>'DailyProfit'!$A$2:$A$47</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$46</f>
+              <f>'DailyProfit'!$H$2:$H$47</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2724,7 +2724,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
@@ -2755,6 +2755,40 @@
       </c>
       <c r="J46" s="11" t="n">
         <v>152726</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n">
+        <v>114340</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>832344</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>16696747</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>10700</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>0.001068598130841121</v>
+      </c>
+      <c r="G47" s="12" t="n">
+        <v>0.007778915887850468</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>0.1560443644859813</v>
+      </c>
+      <c r="I47" s="11" t="n">
+        <v>-38386</v>
+      </c>
+      <c r="J47" s="11" t="n">
+        <v>114340</v>
       </c>
     </row>
   </sheetData>
@@ -2832,7 +2866,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2887,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>152726</v>
+        <v>114340</v>
       </c>
     </row>
     <row r="5">
@@ -2863,7 +2897,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>718004</v>
+        <v>832344</v>
       </c>
     </row>
     <row r="6">
@@ -2873,7 +2907,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16582407</v>
+        <v>16696747</v>
       </c>
     </row>
     <row r="7">
@@ -2883,7 +2917,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001427345794392523</v>
+        <v>0.001068598130841121</v>
       </c>
     </row>
     <row r="8">
@@ -2893,7 +2927,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.006710317757009346</v>
+        <v>0.007778915887850468</v>
       </c>
     </row>
     <row r="9">
@@ -2903,7 +2937,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1549757663551402</v>
+        <v>0.1560443644859813</v>
       </c>
     </row>
     <row r="10">
@@ -2913,7 +2947,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3219554.733333333</v>
+        <v>3152050.065217391</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$47</f>
+              <f>'DailyProfit'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$47</f>
+              <f>'DailyProfit'!$B$2:$B$48</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$47</f>
+              <f>'DailyProfit'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$47</f>
+              <f>'DailyProfit'!$D$2:$D$48</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$47</f>
+              <f>'DailyProfit'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$47</f>
+              <f>'DailyProfit'!$F$2:$F$48</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$47</f>
+              <f>'DailyProfit'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$47</f>
+              <f>'DailyProfit'!$G$2:$G$48</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$47</f>
+              <f>'DailyProfit'!$A$2:$A$48</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$47</f>
+              <f>'DailyProfit'!$H$2:$H$48</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2758,7 +2758,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
@@ -2789,6 +2789,40 @@
       </c>
       <c r="J47" s="11" t="n">
         <v>114340</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n">
+        <v>130454</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>962798</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>16827201</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F48" s="12" t="n">
+        <v>0.001291623762376238</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.009532653465346534</v>
+      </c>
+      <c r="H48" s="12" t="n">
+        <v>0.1666059504950495</v>
+      </c>
+      <c r="I48" s="11" t="n">
+        <v>16114</v>
+      </c>
+      <c r="J48" s="11" t="n">
+        <v>130454</v>
       </c>
     </row>
   </sheetData>
@@ -2866,7 +2900,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2911,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>10700</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="4">
@@ -2887,7 +2921,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>114340</v>
+        <v>130454</v>
       </c>
     </row>
     <row r="5">
@@ -2897,7 +2931,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>832344</v>
+        <v>962798</v>
       </c>
     </row>
     <row r="6">
@@ -2907,7 +2941,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16696747</v>
+        <v>16827201</v>
       </c>
     </row>
     <row r="7">
@@ -2917,7 +2951,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001068598130841121</v>
+        <v>0.001291623762376238</v>
       </c>
     </row>
     <row r="8">
@@ -2927,7 +2961,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.007778915887850468</v>
+        <v>0.009532653465346534</v>
       </c>
     </row>
     <row r="9">
@@ -2937,7 +2971,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1560443644859813</v>
+        <v>0.1666059504950495</v>
       </c>
     </row>
     <row r="10">
@@ -2947,7 +2981,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3152050.065217391</v>
+        <v>3087760.787234043</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$48</f>
+              <f>'DailyProfit'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$48</f>
+              <f>'DailyProfit'!$B$2:$B$49</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$48</f>
+              <f>'DailyProfit'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$48</f>
+              <f>'DailyProfit'!$D$2:$D$49</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$48</f>
+              <f>'DailyProfit'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$48</f>
+              <f>'DailyProfit'!$F$2:$F$49</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$48</f>
+              <f>'DailyProfit'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$48</f>
+              <f>'DailyProfit'!$G$2:$G$49</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$48</f>
+              <f>'DailyProfit'!$A$2:$A$49</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$48</f>
+              <f>'DailyProfit'!$H$2:$H$49</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2792,7 +2792,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
@@ -2823,6 +2823,40 @@
       </c>
       <c r="J48" s="11" t="n">
         <v>130454</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="n">
+        <v>79696</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>1042494</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>16906897</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F49" s="12" t="n">
+        <v>0.0007890693069306931</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.01032172277227723</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>0.1673950198019802</v>
+      </c>
+      <c r="I49" s="11" t="n">
+        <v>-50758</v>
+      </c>
+      <c r="J49" s="11" t="n">
+        <v>79696</v>
       </c>
     </row>
   </sheetData>
@@ -2900,7 +2934,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2955,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>130454</v>
+        <v>79696</v>
       </c>
     </row>
     <row r="5">
@@ -2931,7 +2965,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>962798</v>
+        <v>1042494</v>
       </c>
     </row>
     <row r="6">
@@ -2941,7 +2975,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16827201</v>
+        <v>16906897</v>
       </c>
     </row>
     <row r="7">
@@ -2951,7 +2985,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001291623762376238</v>
+        <v>0.0007890693069306931</v>
       </c>
     </row>
     <row r="8">
@@ -2961,7 +2995,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.009532653465346534</v>
+        <v>0.01032172277227723</v>
       </c>
     </row>
     <row r="9">
@@ -2971,7 +3005,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1666059504950495</v>
+        <v>0.1673950198019802</v>
       </c>
     </row>
     <row r="10">
@@ -2981,7 +3015,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3087760.787234043</v>
+        <v>3025092.770833333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$49</f>
+              <f>'DailyProfit'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$49</f>
+              <f>'DailyProfit'!$B$2:$B$50</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$49</f>
+              <f>'DailyProfit'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$49</f>
+              <f>'DailyProfit'!$D$2:$D$50</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$49</f>
+              <f>'DailyProfit'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$49</f>
+              <f>'DailyProfit'!$F$2:$F$50</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$49</f>
+              <f>'DailyProfit'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$49</f>
+              <f>'DailyProfit'!$G$2:$G$50</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$49</f>
+              <f>'DailyProfit'!$A$2:$A$50</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$49</f>
+              <f>'DailyProfit'!$H$2:$H$50</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2826,7 +2826,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>2026-09-11</t>
         </is>
@@ -2857,6 +2857,40 @@
       </c>
       <c r="J49" s="11" t="n">
         <v>79696</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B50" s="11" t="n">
+        <v>86968</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>1129462</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>16993865</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0.0008610693069306931</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.01118279207920792</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>0.1682560891089109</v>
+      </c>
+      <c r="I50" s="11" t="n">
+        <v>7272</v>
+      </c>
+      <c r="J50" s="11" t="n">
+        <v>86968</v>
       </c>
     </row>
   </sheetData>
@@ -2934,7 +2968,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -2955,7 +2989,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>79696</v>
+        <v>86968</v>
       </c>
     </row>
     <row r="5">
@@ -2965,7 +2999,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1042494</v>
+        <v>1129462</v>
       </c>
     </row>
     <row r="6">
@@ -2975,7 +3009,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16906897</v>
+        <v>16993865</v>
       </c>
     </row>
     <row r="7">
@@ -2985,7 +3019,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0007890693069306931</v>
+        <v>0.0008610693069306931</v>
       </c>
     </row>
     <row r="8">
@@ -2995,7 +3029,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01032172277227723</v>
+        <v>0.01118279207920792</v>
       </c>
     </row>
     <row r="9">
@@ -3005,7 +3039,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1673950198019802</v>
+        <v>0.1682560891089109</v>
       </c>
     </row>
     <row r="10">
@@ -3015,7 +3049,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3025092.770833333</v>
+        <v>2965131.040816327</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$50</f>
+              <f>'DailyProfit'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$50</f>
+              <f>'DailyProfit'!$B$2:$B$51</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$50</f>
+              <f>'DailyProfit'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$50</f>
+              <f>'DailyProfit'!$D$2:$D$51</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$50</f>
+              <f>'DailyProfit'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$50</f>
+              <f>'DailyProfit'!$F$2:$F$51</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$50</f>
+              <f>'DailyProfit'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$50</f>
+              <f>'DailyProfit'!$G$2:$G$51</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$50</f>
+              <f>'DailyProfit'!$A$2:$A$51</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$50</f>
+              <f>'DailyProfit'!$H$2:$H$51</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2860,7 +2860,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
@@ -2891,6 +2891,40 @@
       </c>
       <c r="J50" s="11" t="n">
         <v>86968</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>123187</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>1252649</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>17117052</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>0.001219673267326733</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.01240246534653465</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>0.1694757623762376</v>
+      </c>
+      <c r="I51" s="11" t="n">
+        <v>36219</v>
+      </c>
+      <c r="J51" s="11" t="n">
+        <v>123187</v>
       </c>
     </row>
   </sheetData>
@@ -2968,7 +3002,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -2989,7 +3023,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>86968</v>
+        <v>123187</v>
       </c>
     </row>
     <row r="5">
@@ -2999,7 +3033,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1129462</v>
+        <v>1252649</v>
       </c>
     </row>
     <row r="6">
@@ -3009,7 +3043,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>16993865</v>
+        <v>17117052</v>
       </c>
     </row>
     <row r="7">
@@ -3019,7 +3053,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0008610693069306931</v>
+        <v>0.001219673267326733</v>
       </c>
     </row>
     <row r="8">
@@ -3029,7 +3063,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01118279207920792</v>
+        <v>0.01240246534653465</v>
       </c>
     </row>
     <row r="9">
@@ -3039,7 +3073,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1682560891089109</v>
+        <v>0.1694757623762376</v>
       </c>
     </row>
     <row r="10">
@@ -3049,7 +3083,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2965131.040816327</v>
+        <v>2908292.16</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$51</f>
+              <f>'DailyProfit'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$51</f>
+              <f>'DailyProfit'!$B$2:$B$52</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$51</f>
+              <f>'DailyProfit'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$51</f>
+              <f>'DailyProfit'!$D$2:$D$52</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$51</f>
+              <f>'DailyProfit'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$51</f>
+              <f>'DailyProfit'!$F$2:$F$52</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$51</f>
+              <f>'DailyProfit'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$51</f>
+              <f>'DailyProfit'!$G$2:$G$52</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$51</f>
+              <f>'DailyProfit'!$A$2:$A$52</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$51</f>
+              <f>'DailyProfit'!$H$2:$H$52</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2894,7 +2894,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>2026-09-15</t>
         </is>
@@ -2925,6 +2925,40 @@
       </c>
       <c r="J51" s="11" t="n">
         <v>123187</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B52" s="11" t="n">
+        <v>93871</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>1346520</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>17210923</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F52" s="12" t="n">
+        <v>0.0009294158415841584</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.01333188118811881</v>
+      </c>
+      <c r="H52" s="12" t="n">
+        <v>0.1704051782178218</v>
+      </c>
+      <c r="I52" s="11" t="n">
+        <v>-29316</v>
+      </c>
+      <c r="J52" s="11" t="n">
+        <v>93871</v>
       </c>
     </row>
   </sheetData>
@@ -3002,7 +3036,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -3023,7 +3057,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>123187</v>
+        <v>93871</v>
       </c>
     </row>
     <row r="5">
@@ -3033,7 +3067,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1252649</v>
+        <v>1346520</v>
       </c>
     </row>
     <row r="6">
@@ -3043,7 +3077,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17117052</v>
+        <v>17210923</v>
       </c>
     </row>
     <row r="7">
@@ -3053,7 +3087,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001219673267326733</v>
+        <v>0.0009294158415841584</v>
       </c>
     </row>
     <row r="8">
@@ -3063,7 +3097,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01240246534653465</v>
+        <v>0.01333188118811881</v>
       </c>
     </row>
     <row r="9">
@@ -3073,7 +3107,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1694757623762376</v>
+        <v>0.1704051782178218</v>
       </c>
     </row>
     <row r="10">
@@ -3083,7 +3117,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2908292.16</v>
+        <v>2853107.431372549</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$52</f>
+              <f>'DailyProfit'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$52</f>
+              <f>'DailyProfit'!$B$2:$B$53</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$52</f>
+              <f>'DailyProfit'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$52</f>
+              <f>'DailyProfit'!$D$2:$D$53</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$52</f>
+              <f>'DailyProfit'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$52</f>
+              <f>'DailyProfit'!$F$2:$F$53</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$52</f>
+              <f>'DailyProfit'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$52</f>
+              <f>'DailyProfit'!$G$2:$G$53</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$52</f>
+              <f>'DailyProfit'!$A$2:$A$53</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$52</f>
+              <f>'DailyProfit'!$H$2:$H$53</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2928,7 +2928,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>2026-09-16</t>
         </is>
@@ -2959,6 +2959,40 @@
       </c>
       <c r="J52" s="11" t="n">
         <v>93871</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B53" s="11" t="n">
+        <v>75891</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>1422411</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>17286814</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F53" s="12" t="n">
+        <v>0.0007513960396039604</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.01408327722772277</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>0.1711565742574258</v>
+      </c>
+      <c r="I53" s="11" t="n">
+        <v>-17980</v>
+      </c>
+      <c r="J53" s="11" t="n">
+        <v>75891</v>
       </c>
     </row>
   </sheetData>
@@ -3036,7 +3070,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3091,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>93871</v>
+        <v>75891</v>
       </c>
     </row>
     <row r="5">
@@ -3067,7 +3101,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1346520</v>
+        <v>1422411</v>
       </c>
     </row>
     <row r="6">
@@ -3077,7 +3111,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17210923</v>
+        <v>17286814</v>
       </c>
     </row>
     <row r="7">
@@ -3087,7 +3121,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0009294158415841584</v>
+        <v>0.0007513960396039604</v>
       </c>
     </row>
     <row r="8">
@@ -3097,7 +3131,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01333188118811881</v>
+        <v>0.01408327722772277</v>
       </c>
     </row>
     <row r="9">
@@ -3107,7 +3141,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1704051782178218</v>
+        <v>0.1711565742574258</v>
       </c>
     </row>
     <row r="10">
@@ -3117,7 +3151,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2853107.431372549</v>
+        <v>2799699.423076923</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$53</f>
+              <f>'DailyProfit'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$53</f>
+              <f>'DailyProfit'!$B$2:$B$54</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$53</f>
+              <f>'DailyProfit'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$53</f>
+              <f>'DailyProfit'!$D$2:$D$54</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$53</f>
+              <f>'DailyProfit'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$53</f>
+              <f>'DailyProfit'!$F$2:$F$54</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$53</f>
+              <f>'DailyProfit'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$53</f>
+              <f>'DailyProfit'!$G$2:$G$54</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$53</f>
+              <f>'DailyProfit'!$A$2:$A$54</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$53</f>
+              <f>'DailyProfit'!$H$2:$H$54</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2962,7 +2962,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>2026-09-17</t>
         </is>
@@ -2993,6 +2993,40 @@
       </c>
       <c r="J53" s="11" t="n">
         <v>75891</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>86715</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>1509126</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>43357.5</v>
+      </c>
+      <c r="H54" s="12" t="n">
+        <v>754563</v>
+      </c>
+      <c r="I54" s="11" t="n">
+        <v>-75835</v>
+      </c>
+      <c r="J54" s="11" t="n">
+        <v>-15777688</v>
       </c>
     </row>
   </sheetData>
@@ -3070,7 +3104,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3115,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>10100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3091,7 +3125,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>75891</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5">
@@ -3101,7 +3135,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1422411</v>
+        <v>86715</v>
       </c>
     </row>
     <row r="6">
@@ -3111,7 +3145,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17286814</v>
+        <v>1509126</v>
       </c>
     </row>
     <row r="7">
@@ -3121,7 +3155,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0007513960396039604</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -3131,7 +3165,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01408327722772277</v>
+        <v>43357.5</v>
       </c>
     </row>
     <row r="9">
@@ -3141,7 +3175,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1711565742574258</v>
+        <v>754563</v>
       </c>
     </row>
     <row r="10">
@@ -3151,7 +3185,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2799699.423076923</v>
+        <v>2746875.962264151</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$54</f>
+              <f>'DailyProfit'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$54</f>
+              <f>'DailyProfit'!$B$2:$B$55</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$54</f>
+              <f>'DailyProfit'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$54</f>
+              <f>'DailyProfit'!$D$2:$D$55</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$54</f>
+              <f>'DailyProfit'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$54</f>
+              <f>'DailyProfit'!$F$2:$F$55</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$54</f>
+              <f>'DailyProfit'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$54</f>
+              <f>'DailyProfit'!$G$2:$G$55</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$54</f>
+              <f>'DailyProfit'!$A$2:$A$55</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$54</f>
+              <f>'DailyProfit'!$H$2:$H$55</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -2996,7 +2996,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>2026-09-18</t>
         </is>
@@ -3027,6 +3027,40 @@
       </c>
       <c r="J54" s="11" t="n">
         <v>-15777688</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>94045</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>94045</v>
+      </c>
+      <c r="I55" s="11" t="n">
+        <v>-39</v>
+      </c>
+      <c r="J55" s="11" t="n">
+        <v>-1415081</v>
       </c>
     </row>
   </sheetData>
@@ -3104,7 +3138,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3159,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>56</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -3135,7 +3169,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>86715</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
@@ -3145,7 +3179,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1509126</v>
+        <v>94045</v>
       </c>
     </row>
     <row r="7">
@@ -3155,7 +3189,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -3165,7 +3199,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>43357.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9">
@@ -3175,7 +3209,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>754563</v>
+        <v>94045</v>
       </c>
     </row>
     <row r="10">
@@ -3185,7 +3219,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2746875.962264151</v>
+        <v>2696008.203703704</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$55</f>
+              <f>'DailyProfit'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$55</f>
+              <f>'DailyProfit'!$B$2:$B$56</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$55</f>
+              <f>'DailyProfit'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$55</f>
+              <f>'DailyProfit'!$D$2:$D$56</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$55</f>
+              <f>'DailyProfit'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$55</f>
+              <f>'DailyProfit'!$F$2:$F$56</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$55</f>
+              <f>'DailyProfit'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$55</f>
+              <f>'DailyProfit'!$G$2:$G$56</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$55</f>
+              <f>'DailyProfit'!$A$2:$A$56</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$55</f>
+              <f>'DailyProfit'!$H$2:$H$56</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3030,7 +3030,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>2026-09-21</t>
         </is>
@@ -3061,6 +3061,40 @@
       </c>
       <c r="J55" s="11" t="n">
         <v>-1415081</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n">
+        <v>169938</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>1773109</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>17637512</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F56" s="12" t="n">
+        <v>0.001682554455445545</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.01755553465346535</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>0.1746288316831683</v>
+      </c>
+      <c r="I56" s="11" t="n">
+        <v>169921</v>
+      </c>
+      <c r="J56" s="11" t="n">
+        <v>17543467</v>
       </c>
     </row>
   </sheetData>
@@ -3138,7 +3172,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3183,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="4">
@@ -3159,7 +3193,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>17</v>
+        <v>169938</v>
       </c>
     </row>
     <row r="5">
@@ -3169,7 +3203,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>56</v>
+        <v>1773109</v>
       </c>
     </row>
     <row r="6">
@@ -3179,7 +3213,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>94045</v>
+        <v>17637512</v>
       </c>
     </row>
     <row r="7">
@@ -3189,7 +3223,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>17</v>
+        <v>0.001682554455445545</v>
       </c>
     </row>
     <row r="8">
@@ -3199,7 +3233,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>56</v>
+        <v>0.01755553465346535</v>
       </c>
     </row>
     <row r="9">
@@ -3209,7 +3243,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>94045</v>
+        <v>0.1746288316831683</v>
       </c>
     </row>
     <row r="10">
@@ -3219,7 +3253,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2696008.203703704</v>
+        <v>2650079.654545455</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$56</f>
+              <f>'DailyProfit'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$56</f>
+              <f>'DailyProfit'!$B$2:$B$57</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$56</f>
+              <f>'DailyProfit'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$56</f>
+              <f>'DailyProfit'!$D$2:$D$57</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$56</f>
+              <f>'DailyProfit'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$56</f>
+              <f>'DailyProfit'!$F$2:$F$57</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$56</f>
+              <f>'DailyProfit'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$56</f>
+              <f>'DailyProfit'!$G$2:$G$57</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$56</f>
+              <f>'DailyProfit'!$A$2:$A$57</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$56</f>
+              <f>'DailyProfit'!$H$2:$H$57</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3064,7 +3064,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
@@ -3095,6 +3095,40 @@
       </c>
       <c r="J56" s="11" t="n">
         <v>17543467</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>130206</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>1903315</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>17767718</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F57" s="12" t="n">
+        <v>0.001289168316831683</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.01884470297029703</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>0.175918</v>
+      </c>
+      <c r="I57" s="11" t="n">
+        <v>-39732</v>
+      </c>
+      <c r="J57" s="11" t="n">
+        <v>130206</v>
       </c>
     </row>
   </sheetData>
@@ -3172,7 +3206,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
@@ -3193,7 +3227,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>169938</v>
+        <v>130206</v>
       </c>
     </row>
     <row r="5">
@@ -3203,7 +3237,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1773109</v>
+        <v>1903315</v>
       </c>
     </row>
     <row r="6">
@@ -3213,7 +3247,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17637512</v>
+        <v>17767718</v>
       </c>
     </row>
     <row r="7">
@@ -3223,7 +3257,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001682554455445545</v>
+        <v>0.001289168316831683</v>
       </c>
     </row>
     <row r="8">
@@ -3233,7 +3267,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01755553465346535</v>
+        <v>0.01884470297029703</v>
       </c>
     </row>
     <row r="9">
@@ -3243,7 +3277,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1746288316831683</v>
+        <v>0.175918</v>
       </c>
     </row>
     <row r="10">
@@ -3253,7 +3287,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2650079.654545455</v>
+        <v>2605081.910714286</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$57</f>
+              <f>'DailyProfit'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$57</f>
+              <f>'DailyProfit'!$B$2:$B$58</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$57</f>
+              <f>'DailyProfit'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$57</f>
+              <f>'DailyProfit'!$D$2:$D$58</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$57</f>
+              <f>'DailyProfit'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$57</f>
+              <f>'DailyProfit'!$F$2:$F$58</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$57</f>
+              <f>'DailyProfit'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$57</f>
+              <f>'DailyProfit'!$G$2:$G$58</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$57</f>
+              <f>'DailyProfit'!$A$2:$A$58</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$57</f>
+              <f>'DailyProfit'!$H$2:$H$58</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3098,7 +3098,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -3129,6 +3129,40 @@
       </c>
       <c r="J57" s="11" t="n">
         <v>130206</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n">
+        <v>180802</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>2084117</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>17948520</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F58" s="12" t="n">
+        <v>0.001790118811881188</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.02063482178217822</v>
+      </c>
+      <c r="H58" s="12" t="n">
+        <v>0.1777081188118812</v>
+      </c>
+      <c r="I58" s="11" t="n">
+        <v>50596</v>
+      </c>
+      <c r="J58" s="11" t="n">
+        <v>180802</v>
       </c>
     </row>
   </sheetData>
@@ -3206,7 +3240,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3261,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>130206</v>
+        <v>180802</v>
       </c>
     </row>
     <row r="5">
@@ -3237,7 +3271,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1903315</v>
+        <v>2084117</v>
       </c>
     </row>
     <row r="6">
@@ -3247,7 +3281,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17767718</v>
+        <v>17948520</v>
       </c>
     </row>
     <row r="7">
@@ -3257,7 +3291,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001289168316831683</v>
+        <v>0.001790118811881188</v>
       </c>
     </row>
     <row r="8">
@@ -3267,7 +3301,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01884470297029703</v>
+        <v>0.02063482178217822</v>
       </c>
     </row>
     <row r="9">
@@ -3277,7 +3311,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.175918</v>
+        <v>0.1777081188118812</v>
       </c>
     </row>
     <row r="10">
@@ -3287,7 +3321,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2605081.910714286</v>
+        <v>2562550.684210526</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$58</f>
+              <f>'DailyProfit'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$58</f>
+              <f>'DailyProfit'!$B$2:$B$59</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$58</f>
+              <f>'DailyProfit'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$58</f>
+              <f>'DailyProfit'!$D$2:$D$59</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$58</f>
+              <f>'DailyProfit'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$58</f>
+              <f>'DailyProfit'!$F$2:$F$59</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$58</f>
+              <f>'DailyProfit'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$58</f>
+              <f>'DailyProfit'!$G$2:$G$59</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$58</f>
+              <f>'DailyProfit'!$A$2:$A$59</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$58</f>
+              <f>'DailyProfit'!$H$2:$H$59</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3132,7 +3132,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
@@ -3163,6 +3163,40 @@
       </c>
       <c r="J58" s="11" t="n">
         <v>180802</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>108600</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>2192717</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>18057120</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>0.001075247524752475</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.02171006930693069</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>0.1787833663366337</v>
+      </c>
+      <c r="I59" s="11" t="n">
+        <v>-72202</v>
+      </c>
+      <c r="J59" s="11" t="n">
+        <v>108600</v>
       </c>
     </row>
   </sheetData>
@@ -3240,7 +3274,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -3261,7 +3295,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>180802</v>
+        <v>108600</v>
       </c>
     </row>
     <row r="5">
@@ -3271,7 +3305,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2084117</v>
+        <v>2192717</v>
       </c>
     </row>
     <row r="6">
@@ -3281,7 +3315,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>17948520</v>
+        <v>18057120</v>
       </c>
     </row>
     <row r="7">
@@ -3291,7 +3325,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001790118811881188</v>
+        <v>0.001075247524752475</v>
       </c>
     </row>
     <row r="8">
@@ -3301,7 +3335,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02063482178217822</v>
+        <v>0.02171006930693069</v>
       </c>
     </row>
     <row r="9">
@@ -3311,7 +3345,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1777081188118812</v>
+        <v>0.1787833663366337</v>
       </c>
     </row>
     <row r="10">
@@ -3321,7 +3355,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2562550.684210526</v>
+        <v>2520241.189655173</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$59</f>
+              <f>'DailyProfit'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$59</f>
+              <f>'DailyProfit'!$B$2:$B$60</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$59</f>
+              <f>'DailyProfit'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$59</f>
+              <f>'DailyProfit'!$D$2:$D$60</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$59</f>
+              <f>'DailyProfit'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$59</f>
+              <f>'DailyProfit'!$F$2:$F$60</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$59</f>
+              <f>'DailyProfit'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$59</f>
+              <f>'DailyProfit'!$G$2:$G$60</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$59</f>
+              <f>'DailyProfit'!$A$2:$A$60</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$59</f>
+              <f>'DailyProfit'!$H$2:$H$60</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3166,7 +3166,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
@@ -3197,6 +3197,40 @@
       </c>
       <c r="J59" s="11" t="n">
         <v>108600</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>130118</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>2322835</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>65059</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>1161417.5</v>
+      </c>
+      <c r="I60" s="11" t="n">
+        <v>-108545</v>
+      </c>
+      <c r="J60" s="11" t="n">
+        <v>-15734285</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3308,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3319,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>10100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3295,7 +3329,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>108600</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -3305,7 +3339,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2192717</v>
+        <v>130118</v>
       </c>
     </row>
     <row r="6">
@@ -3315,7 +3349,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18057120</v>
+        <v>2322835</v>
       </c>
     </row>
     <row r="7">
@@ -3325,7 +3359,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001075247524752475</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8">
@@ -3335,7 +3369,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02171006930693069</v>
+        <v>65059</v>
       </c>
     </row>
     <row r="9">
@@ -3345,7 +3379,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1787833663366337</v>
+        <v>1161417.5</v>
       </c>
     </row>
     <row r="10">
@@ -3355,7 +3389,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2520241.189655173</v>
+        <v>2477526.169491525</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$60</f>
+              <f>'DailyProfit'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$60</f>
+              <f>'DailyProfit'!$B$2:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$60</f>
+              <f>'DailyProfit'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$60</f>
+              <f>'DailyProfit'!$D$2:$D$61</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$60</f>
+              <f>'DailyProfit'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$60</f>
+              <f>'DailyProfit'!$F$2:$F$61</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$60</f>
+              <f>'DailyProfit'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$60</f>
+              <f>'DailyProfit'!$G$2:$G$61</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$60</f>
+              <f>'DailyProfit'!$A$2:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$60</f>
+              <f>'DailyProfit'!$H$2:$H$61</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3200,7 +3200,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
@@ -3231,6 +3231,40 @@
       </c>
       <c r="J60" s="11" t="n">
         <v>-15734285</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>187408</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>187408</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>18374646</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>0.001855524752475248</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.001855524752475248</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>0.1819271881188119</v>
+      </c>
+      <c r="I61" s="11" t="n">
+        <v>187353</v>
+      </c>
+      <c r="J61" s="11" t="n">
+        <v>16051811</v>
       </c>
     </row>
   </sheetData>
@@ -3308,7 +3342,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -3319,7 +3353,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>10100</v>
       </c>
     </row>
     <row r="4">
@@ -3329,7 +3363,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>55</v>
+        <v>187408</v>
       </c>
     </row>
     <row r="5">
@@ -3339,7 +3373,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>130118</v>
+        <v>187408</v>
       </c>
     </row>
     <row r="6">
@@ -3349,7 +3383,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>2322835</v>
+        <v>18374646</v>
       </c>
     </row>
     <row r="7">
@@ -3359,7 +3393,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>27.5</v>
+        <v>0.001855524752475248</v>
       </c>
     </row>
     <row r="8">
@@ -3369,7 +3403,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>65059</v>
+        <v>0.001855524752475248</v>
       </c>
     </row>
     <row r="9">
@@ -3379,7 +3413,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>1161417.5</v>
+        <v>0.1819271881188119</v>
       </c>
     </row>
     <row r="10">
@@ -3389,7 +3423,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2477526.169491525</v>
+        <v>2439357.533333333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$61</f>
+              <f>'DailyProfit'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$61</f>
+              <f>'DailyProfit'!$B$2:$B$62</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$61</f>
+              <f>'DailyProfit'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$61</f>
+              <f>'DailyProfit'!$D$2:$D$62</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$61</f>
+              <f>'DailyProfit'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$61</f>
+              <f>'DailyProfit'!$F$2:$F$62</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$61</f>
+              <f>'DailyProfit'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$61</f>
+              <f>'DailyProfit'!$G$2:$G$62</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$61</f>
+              <f>'DailyProfit'!$A$2:$A$62</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$61</f>
+              <f>'DailyProfit'!$H$2:$H$62</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3234,7 +3234,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
@@ -3265,6 +3265,40 @@
       </c>
       <c r="J61" s="11" t="n">
         <v>16051811</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>64817</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>252225</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>18439463</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>0.0006417524752475247</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.002497277227722772</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>0.1825689405940594</v>
+      </c>
+      <c r="I62" s="11" t="n">
+        <v>-122591</v>
+      </c>
+      <c r="J62" s="11" t="n">
+        <v>64817</v>
       </c>
     </row>
   </sheetData>
@@ -3342,7 +3376,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3397,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>187408</v>
+        <v>64817</v>
       </c>
     </row>
     <row r="5">
@@ -3373,7 +3407,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>187408</v>
+        <v>252225</v>
       </c>
     </row>
     <row r="6">
@@ -3383,7 +3417,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18374646</v>
+        <v>18439463</v>
       </c>
     </row>
     <row r="7">
@@ -3393,7 +3427,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001855524752475248</v>
+        <v>0.0006417524752475247</v>
       </c>
     </row>
     <row r="8">
@@ -3403,7 +3437,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.001855524752475248</v>
+        <v>0.002497277227722772</v>
       </c>
     </row>
     <row r="9">
@@ -3413,7 +3447,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1819271881188119</v>
+        <v>0.1825689405940594</v>
       </c>
     </row>
     <row r="10">
@@ -3423,7 +3457,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2439357.533333333</v>
+        <v>2400430.639344262</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$62</f>
+              <f>'DailyProfit'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$62</f>
+              <f>'DailyProfit'!$B$2:$B$63</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$62</f>
+              <f>'DailyProfit'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$62</f>
+              <f>'DailyProfit'!$D$2:$D$63</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$62</f>
+              <f>'DailyProfit'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$62</f>
+              <f>'DailyProfit'!$F$2:$F$63</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$62</f>
+              <f>'DailyProfit'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$62</f>
+              <f>'DailyProfit'!$G$2:$G$63</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$62</f>
+              <f>'DailyProfit'!$A$2:$A$63</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$62</f>
+              <f>'DailyProfit'!$H$2:$H$63</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3268,7 +3268,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
@@ -3299,6 +3299,40 @@
       </c>
       <c r="J62" s="11" t="n">
         <v>64817</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>143855</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>396080</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>18583318</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>0.001424306930693069</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.003921584158415842</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>0.1839932475247525</v>
+      </c>
+      <c r="I63" s="11" t="n">
+        <v>79038</v>
+      </c>
+      <c r="J63" s="11" t="n">
+        <v>143855</v>
       </c>
     </row>
   </sheetData>
@@ -3376,7 +3410,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3431,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>64817</v>
+        <v>143855</v>
       </c>
     </row>
     <row r="5">
@@ -3407,7 +3441,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>252225</v>
+        <v>396080</v>
       </c>
     </row>
     <row r="6">
@@ -3417,7 +3451,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18439463</v>
+        <v>18583318</v>
       </c>
     </row>
     <row r="7">
@@ -3427,7 +3461,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0006417524752475247</v>
+        <v>0.001424306930693069</v>
       </c>
     </row>
     <row r="8">
@@ -3437,7 +3471,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.002497277227722772</v>
+        <v>0.003921584158415842</v>
       </c>
     </row>
     <row r="9">
@@ -3447,7 +3481,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1825689405940594</v>
+        <v>0.1839932475247525</v>
       </c>
     </row>
     <row r="10">
@@ -3457,7 +3491,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2400430.639344262</v>
+        <v>2364034.258064516</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$63</f>
+              <f>'DailyProfit'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$63</f>
+              <f>'DailyProfit'!$B$2:$B$64</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$63</f>
+              <f>'DailyProfit'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$63</f>
+              <f>'DailyProfit'!$D$2:$D$64</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$63</f>
+              <f>'DailyProfit'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$63</f>
+              <f>'DailyProfit'!$F$2:$F$64</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$63</f>
+              <f>'DailyProfit'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$63</f>
+              <f>'DailyProfit'!$G$2:$G$64</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$63</f>
+              <f>'DailyProfit'!$A$2:$A$64</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$63</f>
+              <f>'DailyProfit'!$H$2:$H$64</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3302,7 +3302,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>2026-10-06</t>
         </is>
@@ -3333,6 +3333,40 @@
       </c>
       <c r="J63" s="11" t="n">
         <v>143855</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
+        <v>158247</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>554327</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>18741565</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>0.00156680198019802</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>0.005488386138613861</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>0.1855600495049505</v>
+      </c>
+      <c r="I64" s="11" t="n">
+        <v>14392</v>
+      </c>
+      <c r="J64" s="11" t="n">
+        <v>158247</v>
       </c>
     </row>
   </sheetData>
@@ -3410,7 +3444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3465,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>143855</v>
+        <v>158247</v>
       </c>
     </row>
     <row r="5">
@@ -3441,7 +3475,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>396080</v>
+        <v>554327</v>
       </c>
     </row>
     <row r="6">
@@ -3451,7 +3485,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18583318</v>
+        <v>18741565</v>
       </c>
     </row>
     <row r="7">
@@ -3461,7 +3495,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001424306930693069</v>
+        <v>0.00156680198019802</v>
       </c>
     </row>
     <row r="8">
@@ -3471,7 +3505,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.003921584158415842</v>
+        <v>0.005488386138613861</v>
       </c>
     </row>
     <row r="9">
@@ -3481,7 +3515,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1839932475247525</v>
+        <v>0.1855600495049505</v>
       </c>
     </row>
     <row r="10">
@@ -3491,7 +3525,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2364034.258064516</v>
+        <v>2329021.761904762</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$64</f>
+              <f>'DailyProfit'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$64</f>
+              <f>'DailyProfit'!$B$2:$B$65</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$64</f>
+              <f>'DailyProfit'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$64</f>
+              <f>'DailyProfit'!$D$2:$D$65</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$64</f>
+              <f>'DailyProfit'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$64</f>
+              <f>'DailyProfit'!$F$2:$F$65</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$64</f>
+              <f>'DailyProfit'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$64</f>
+              <f>'DailyProfit'!$G$2:$G$65</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$64</f>
+              <f>'DailyProfit'!$A$2:$A$65</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$64</f>
+              <f>'DailyProfit'!$H$2:$H$65</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3336,7 +3336,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>2026-10-07</t>
         </is>
@@ -3367,6 +3367,40 @@
       </c>
       <c r="J64" s="11" t="n">
         <v>158247</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>147536</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>701863</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>18889101</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>10100</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>0.001460752475247525</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.006949138613861386</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>0.187020801980198</v>
+      </c>
+      <c r="I65" s="11" t="n">
+        <v>-10711</v>
+      </c>
+      <c r="J65" s="11" t="n">
+        <v>147536</v>
       </c>
     </row>
   </sheetData>
@@ -3444,7 +3478,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -3465,7 +3499,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>158247</v>
+        <v>147536</v>
       </c>
     </row>
     <row r="5">
@@ -3475,7 +3509,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>554327</v>
+        <v>701863</v>
       </c>
     </row>
     <row r="6">
@@ -3485,7 +3519,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18741565</v>
+        <v>18889101</v>
       </c>
     </row>
     <row r="7">
@@ -3495,7 +3529,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.00156680198019802</v>
+        <v>0.001460752475247525</v>
       </c>
     </row>
     <row r="8">
@@ -3505,7 +3539,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.005488386138613861</v>
+        <v>0.006949138613861386</v>
       </c>
     </row>
     <row r="9">
@@ -3515,7 +3549,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.1855600495049505</v>
+        <v>0.187020801980198</v>
       </c>
     </row>
     <row r="10">
@@ -3525,7 +3559,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2329021.761904762</v>
+        <v>2294936.046875</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$65</f>
+              <f>'DailyProfit'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$65</f>
+              <f>'DailyProfit'!$B$2:$B$66</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$65</f>
+              <f>'DailyProfit'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$65</f>
+              <f>'DailyProfit'!$D$2:$D$66</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$65</f>
+              <f>'DailyProfit'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$65</f>
+              <f>'DailyProfit'!$F$2:$F$66</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$65</f>
+              <f>'DailyProfit'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$65</f>
+              <f>'DailyProfit'!$G$2:$G$66</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$65</f>
+              <f>'DailyProfit'!$A$2:$A$66</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$65</f>
+              <f>'DailyProfit'!$H$2:$H$66</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3370,7 +3370,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
@@ -3401,6 +3401,40 @@
       </c>
       <c r="J65" s="11" t="n">
         <v>147536</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>257820</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>1154631</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>128910</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>577315.5</v>
+      </c>
+      <c r="I66" s="11" t="n">
+        <v>-147481</v>
+      </c>
+      <c r="J66" s="11" t="n">
+        <v>-17734470</v>
       </c>
     </row>
   </sheetData>
@@ -3478,7 +3512,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3523,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>10100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3499,7 +3533,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>147536</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
@@ -3509,7 +3543,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>701863</v>
+        <v>257820</v>
       </c>
     </row>
     <row r="6">
@@ -3519,7 +3553,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>18889101</v>
+        <v>1154631</v>
       </c>
     </row>
     <row r="7">
@@ -3529,7 +3563,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001460752475247525</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8">
@@ -3539,7 +3573,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.006949138613861386</v>
+        <v>128910</v>
       </c>
     </row>
     <row r="9">
@@ -3549,7 +3583,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.187020801980198</v>
+        <v>577315.5</v>
       </c>
     </row>
     <row r="10">
@@ -3559,7 +3593,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2294936.046875</v>
+        <v>2259630.184615385</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$66</f>
+              <f>'DailyProfit'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$66</f>
+              <f>'DailyProfit'!$B$2:$B$67</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$66</f>
+              <f>'DailyProfit'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$66</f>
+              <f>'DailyProfit'!$D$2:$D$67</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$66</f>
+              <f>'DailyProfit'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$66</f>
+              <f>'DailyProfit'!$F$2:$F$67</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$66</f>
+              <f>'DailyProfit'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$66</f>
+              <f>'DailyProfit'!$G$2:$G$67</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$66</f>
+              <f>'DailyProfit'!$A$2:$A$67</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$66</f>
+              <f>'DailyProfit'!$H$2:$H$67</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J66"/>
+  <dimension ref="A1:J67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3404,7 +3404,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
@@ -3435,6 +3435,40 @@
       </c>
       <c r="J66" s="11" t="n">
         <v>-17734470</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>139261</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>1293892</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>69630.5</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>646946</v>
+      </c>
+      <c r="I67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="11" t="n">
+        <v>139261</v>
       </c>
     </row>
   </sheetData>
@@ -3512,7 +3546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -3543,7 +3577,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>257820</v>
+        <v>139261</v>
       </c>
     </row>
     <row r="6">
@@ -3553,7 +3587,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1154631</v>
+        <v>1293892</v>
       </c>
     </row>
     <row r="7">
@@ -3573,7 +3607,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>128910</v>
+        <v>69630.5</v>
       </c>
     </row>
     <row r="9">
@@ -3583,7 +3617,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>577315.5</v>
+        <v>646946</v>
       </c>
     </row>
     <row r="10">
@@ -3593,7 +3627,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2259630.184615385</v>
+        <v>2225394.196969697</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$67</f>
+              <f>'DailyProfit'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$67</f>
+              <f>'DailyProfit'!$B$2:$B$68</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$67</f>
+              <f>'DailyProfit'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$67</f>
+              <f>'DailyProfit'!$D$2:$D$68</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$67</f>
+              <f>'DailyProfit'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$67</f>
+              <f>'DailyProfit'!$F$2:$F$68</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$67</f>
+              <f>'DailyProfit'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$67</f>
+              <f>'DailyProfit'!$G$2:$G$68</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$67</f>
+              <f>'DailyProfit'!$A$2:$A$68</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$67</f>
+              <f>'DailyProfit'!$H$2:$H$68</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J67"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3438,7 +3438,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>2026-10-14</t>
         </is>
@@ -3469,6 +3469,40 @@
       </c>
       <c r="J67" s="11" t="n">
         <v>139261</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>117045390</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>117045390</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I68" s="11" t="n">
+        <v>3699945</v>
+      </c>
+      <c r="J68" s="11" t="n">
+        <v>-1293872</v>
       </c>
     </row>
   </sheetData>
@@ -3546,7 +3580,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3601,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>55</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="5">
@@ -3577,7 +3611,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>139261</v>
+        <v>117045390</v>
       </c>
     </row>
     <row r="6">
@@ -3587,7 +3621,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>1293892</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -3597,7 +3631,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>27.5</v>
+        <v>3700000</v>
       </c>
     </row>
     <row r="8">
@@ -3607,7 +3641,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>69630.5</v>
+        <v>117045390</v>
       </c>
     </row>
     <row r="9">
@@ -3617,7 +3651,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>646946</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -3627,7 +3661,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2225394.196969697</v>
+        <v>2247403.23880597</v>
       </c>
     </row>
     <row r="11">
@@ -3691,7 +3725,7 @@
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>-0.9999945432133112</v>
+        <v>-0.9999989411883604</v>
       </c>
     </row>
   </sheetData>

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$68</f>
+              <f>'DailyProfit'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$68</f>
+              <f>'DailyProfit'!$B$2:$B$69</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$68</f>
+              <f>'DailyProfit'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$68</f>
+              <f>'DailyProfit'!$D$2:$D$69</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$68</f>
+              <f>'DailyProfit'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$68</f>
+              <f>'DailyProfit'!$F$2:$F$69</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$68</f>
+              <f>'DailyProfit'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$68</f>
+              <f>'DailyProfit'!$G$2:$G$69</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$68</f>
+              <f>'DailyProfit'!$A$2:$A$69</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$68</f>
+              <f>'DailyProfit'!$H$2:$H$69</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3472,7 +3472,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
@@ -3503,6 +3503,40 @@
       </c>
       <c r="J68" s="11" t="n">
         <v>-1293872</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B69" s="11" t="n">
+        <v>145986</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>1704138</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>19891376</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>0.001500369989722508</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.01751426515930113</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>0.2044334635149024</v>
+      </c>
+      <c r="I69" s="11" t="n">
+        <v>-3554014</v>
+      </c>
+      <c r="J69" s="11" t="n">
+        <v>19891356</v>
       </c>
     </row>
   </sheetData>
@@ -3580,7 +3614,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-16</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3625,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>0</v>
+        <v>9730</v>
       </c>
     </row>
     <row r="4">
@@ -3601,7 +3635,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>3700000</v>
+        <v>145986</v>
       </c>
     </row>
     <row r="5">
@@ -3611,7 +3645,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>117045390</v>
+        <v>1704138</v>
       </c>
     </row>
     <row r="6">
@@ -3621,7 +3655,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20</v>
+        <v>19891376</v>
       </c>
     </row>
     <row r="7">
@@ -3631,7 +3665,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>3700000</v>
+        <v>0.001500369989722508</v>
       </c>
     </row>
     <row r="8">
@@ -3641,7 +3675,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>117045390</v>
+        <v>0.01751426515930113</v>
       </c>
     </row>
     <row r="9">
@@ -3651,7 +3685,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>20</v>
+        <v>0.2044334635149024</v>
       </c>
     </row>
     <row r="10">
@@ -3661,7 +3695,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2247403.23880597</v>
+        <v>2216500.044117647</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$69</f>
+              <f>'DailyProfit'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$69</f>
+              <f>'DailyProfit'!$B$2:$B$70</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$69</f>
+              <f>'DailyProfit'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$69</f>
+              <f>'DailyProfit'!$D$2:$D$70</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$69</f>
+              <f>'DailyProfit'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$69</f>
+              <f>'DailyProfit'!$F$2:$F$70</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$69</f>
+              <f>'DailyProfit'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$69</f>
+              <f>'DailyProfit'!$G$2:$G$70</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$69</f>
+              <f>'DailyProfit'!$A$2:$A$70</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$69</f>
+              <f>'DailyProfit'!$H$2:$H$70</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J69"/>
+  <dimension ref="A1:J70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3506,7 +3506,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>2026-10-16</t>
         </is>
@@ -3537,6 +3537,40 @@
       </c>
       <c r="J69" s="11" t="n">
         <v>19891356</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B70" s="11" t="n">
+        <v>159782</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>1863920</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>20051158</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>0.001642158273381295</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.01915642343268243</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>0.2060756217882836</v>
+      </c>
+      <c r="I70" s="11" t="n">
+        <v>13796</v>
+      </c>
+      <c r="J70" s="11" t="n">
+        <v>159782</v>
       </c>
     </row>
   </sheetData>
@@ -3614,7 +3648,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-16</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3669,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>145986</v>
+        <v>159782</v>
       </c>
     </row>
     <row r="5">
@@ -3645,7 +3679,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1704138</v>
+        <v>1863920</v>
       </c>
     </row>
     <row r="6">
@@ -3655,7 +3689,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>19891376</v>
+        <v>20051158</v>
       </c>
     </row>
     <row r="7">
@@ -3665,7 +3699,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001500369989722508</v>
+        <v>0.001642158273381295</v>
       </c>
     </row>
     <row r="8">
@@ -3675,7 +3709,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01751426515930113</v>
+        <v>0.01915642343268243</v>
       </c>
     </row>
     <row r="9">
@@ -3685,7 +3719,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2044334635149024</v>
+        <v>0.2060756217882836</v>
       </c>
     </row>
     <row r="10">
@@ -3695,7 +3729,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2216500.044117647</v>
+        <v>2186692.536231884</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$70</f>
+              <f>'DailyProfit'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$70</f>
+              <f>'DailyProfit'!$B$2:$B$71</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$70</f>
+              <f>'DailyProfit'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$70</f>
+              <f>'DailyProfit'!$D$2:$D$71</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$70</f>
+              <f>'DailyProfit'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$70</f>
+              <f>'DailyProfit'!$F$2:$F$71</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$70</f>
+              <f>'DailyProfit'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$70</f>
+              <f>'DailyProfit'!$G$2:$G$71</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$70</f>
+              <f>'DailyProfit'!$A$2:$A$71</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$70</f>
+              <f>'DailyProfit'!$H$2:$H$71</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:J71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3540,7 +3540,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>2026-10-19</t>
         </is>
@@ -3571,6 +3571,40 @@
       </c>
       <c r="J70" s="11" t="n">
         <v>159782</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>166685</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>2030605</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>20217843</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>0.001713103802672148</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.02086952723535457</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>0.2077887255909558</v>
+      </c>
+      <c r="I71" s="11" t="n">
+        <v>6903</v>
+      </c>
+      <c r="J71" s="11" t="n">
+        <v>166685</v>
       </c>
     </row>
   </sheetData>
@@ -3648,7 +3682,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3703,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>159782</v>
+        <v>166685</v>
       </c>
     </row>
     <row r="5">
@@ -3679,7 +3713,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>1863920</v>
+        <v>2030605</v>
       </c>
     </row>
     <row r="6">
@@ -3689,7 +3723,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20051158</v>
+        <v>20217843</v>
       </c>
     </row>
     <row r="7">
@@ -3699,7 +3733,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001642158273381295</v>
+        <v>0.001713103802672148</v>
       </c>
     </row>
     <row r="8">
@@ -3709,7 +3743,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.01915642343268243</v>
+        <v>0.02086952723535457</v>
       </c>
     </row>
     <row r="9">
@@ -3719,7 +3753,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2060756217882836</v>
+        <v>0.2077887255909558</v>
       </c>
     </row>
     <row r="10">
@@ -3729,7 +3763,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2186692.536231884</v>
+        <v>2157835.285714286</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$71</f>
+              <f>'DailyProfit'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$71</f>
+              <f>'DailyProfit'!$B$2:$B$72</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$71</f>
+              <f>'DailyProfit'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$71</f>
+              <f>'DailyProfit'!$D$2:$D$72</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$71</f>
+              <f>'DailyProfit'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$71</f>
+              <f>'DailyProfit'!$F$2:$F$72</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$71</f>
+              <f>'DailyProfit'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$71</f>
+              <f>'DailyProfit'!$G$2:$G$72</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$71</f>
+              <f>'DailyProfit'!$A$2:$A$72</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$71</f>
+              <f>'DailyProfit'!$H$2:$H$72</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J71"/>
+  <dimension ref="A1:J72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3574,7 +3574,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>2026-10-20</t>
         </is>
@@ -3605,6 +3605,40 @@
       </c>
       <c r="J71" s="11" t="n">
         <v>166685</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="n">
+        <v>156129</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>2186734</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>20373972</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>0.001604614594039055</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.02247414182939363</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0.2093933401849949</v>
+      </c>
+      <c r="I72" s="11" t="n">
+        <v>-10556</v>
+      </c>
+      <c r="J72" s="11" t="n">
+        <v>156129</v>
       </c>
     </row>
   </sheetData>
@@ -3682,7 +3716,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3737,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>166685</v>
+        <v>156129</v>
       </c>
     </row>
     <row r="5">
@@ -3713,7 +3747,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2030605</v>
+        <v>2186734</v>
       </c>
     </row>
     <row r="6">
@@ -3723,7 +3757,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20217843</v>
+        <v>20373972</v>
       </c>
     </row>
     <row r="7">
@@ -3733,7 +3767,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001713103802672148</v>
+        <v>0.001604614594039055</v>
       </c>
     </row>
     <row r="8">
@@ -3743,7 +3777,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02086952723535457</v>
+        <v>0.02247414182939363</v>
       </c>
     </row>
     <row r="9">
@@ -3753,7 +3787,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2077887255909558</v>
+        <v>0.2093933401849949</v>
       </c>
     </row>
     <row r="10">
@@ -3763,7 +3797,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2157835.285714286</v>
+        <v>2129642.23943662</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$72</f>
+              <f>'DailyProfit'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$72</f>
+              <f>'DailyProfit'!$B$2:$B$73</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$72</f>
+              <f>'DailyProfit'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$72</f>
+              <f>'DailyProfit'!$D$2:$D$73</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$72</f>
+              <f>'DailyProfit'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$72</f>
+              <f>'DailyProfit'!$F$2:$F$73</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$72</f>
+              <f>'DailyProfit'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$72</f>
+              <f>'DailyProfit'!$G$2:$G$73</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$72</f>
+              <f>'DailyProfit'!$A$2:$A$73</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$72</f>
+              <f>'DailyProfit'!$H$2:$H$73</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J72"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3608,7 +3608,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>2026-10-21</t>
         </is>
@@ -3639,6 +3639,40 @@
       </c>
       <c r="J72" s="11" t="n">
         <v>156129</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>215040</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>2401774</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>20589012</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>0.002210071942446043</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.02468421377183967</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0.2116034121274409</v>
+      </c>
+      <c r="I73" s="11" t="n">
+        <v>58911</v>
+      </c>
+      <c r="J73" s="11" t="n">
+        <v>215040</v>
       </c>
     </row>
   </sheetData>
@@ -3716,7 +3750,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3771,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>156129</v>
+        <v>215040</v>
       </c>
     </row>
     <row r="5">
@@ -3747,7 +3781,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2186734</v>
+        <v>2401774</v>
       </c>
     </row>
     <row r="6">
@@ -3757,7 +3791,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20373972</v>
+        <v>20589012</v>
       </c>
     </row>
     <row r="7">
@@ -3767,7 +3801,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001604614594039055</v>
+        <v>0.002210071942446043</v>
       </c>
     </row>
     <row r="8">
@@ -3777,7 +3811,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02247414182939363</v>
+        <v>0.02468421377183967</v>
       </c>
     </row>
     <row r="9">
@@ -3787,7 +3821,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2093933401849949</v>
+        <v>0.2116034121274409</v>
       </c>
     </row>
     <row r="10">
@@ -3797,7 +3831,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2129642.23943662</v>
+        <v>2103050.541666667</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$73</f>
+              <f>'DailyProfit'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$73</f>
+              <f>'DailyProfit'!$B$2:$B$74</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$73</f>
+              <f>'DailyProfit'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$73</f>
+              <f>'DailyProfit'!$D$2:$D$74</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$73</f>
+              <f>'DailyProfit'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$73</f>
+              <f>'DailyProfit'!$F$2:$F$74</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$73</f>
+              <f>'DailyProfit'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$73</f>
+              <f>'DailyProfit'!$G$2:$G$74</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$73</f>
+              <f>'DailyProfit'!$A$2:$A$74</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$73</f>
+              <f>'DailyProfit'!$H$2:$H$74</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3642,7 +3642,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
@@ -3673,6 +3673,40 @@
       </c>
       <c r="J73" s="11" t="n">
         <v>215040</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>193334</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>2595108</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>20782346</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>0.001986988694758479</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.02667120246659815</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>0.2135904008221994</v>
+      </c>
+      <c r="I74" s="11" t="n">
+        <v>-21706</v>
+      </c>
+      <c r="J74" s="11" t="n">
+        <v>193334</v>
       </c>
     </row>
   </sheetData>
@@ -3750,7 +3784,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
     </row>
@@ -3771,7 +3805,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>215040</v>
+        <v>193334</v>
       </c>
     </row>
     <row r="5">
@@ -3781,7 +3815,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2401774</v>
+        <v>2595108</v>
       </c>
     </row>
     <row r="6">
@@ -3791,7 +3825,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20589012</v>
+        <v>20782346</v>
       </c>
     </row>
     <row r="7">
@@ -3801,7 +3835,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.002210071942446043</v>
+        <v>0.001986988694758479</v>
       </c>
     </row>
     <row r="8">
@@ -3811,7 +3845,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02468421377183967</v>
+        <v>0.02667120246659815</v>
       </c>
     </row>
     <row r="9">
@@ -3821,7 +3855,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2116034121274409</v>
+        <v>0.2135904008221994</v>
       </c>
     </row>
     <row r="10">
@@ -3831,7 +3865,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2103050.541666667</v>
+        <v>2076890.04109589</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$74</f>
+              <f>'DailyProfit'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$74</f>
+              <f>'DailyProfit'!$B$2:$B$75</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$74</f>
+              <f>'DailyProfit'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$74</f>
+              <f>'DailyProfit'!$D$2:$D$75</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$74</f>
+              <f>'DailyProfit'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$74</f>
+              <f>'DailyProfit'!$F$2:$F$75</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$74</f>
+              <f>'DailyProfit'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$74</f>
+              <f>'DailyProfit'!$G$2:$G$75</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$74</f>
+              <f>'DailyProfit'!$A$2:$A$75</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$74</f>
+              <f>'DailyProfit'!$H$2:$H$75</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J74"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3676,7 +3676,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>2026-10-23</t>
         </is>
@@ -3707,6 +3707,40 @@
       </c>
       <c r="J74" s="11" t="n">
         <v>193334</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>69044</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>2664152</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>20851390</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>0.0007095991778006167</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.02738080164439877</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>0.2143</v>
+      </c>
+      <c r="I75" s="11" t="n">
+        <v>-124290</v>
+      </c>
+      <c r="J75" s="11" t="n">
+        <v>69044</v>
       </c>
     </row>
   </sheetData>
@@ -3784,7 +3818,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>2026-10-26</t>
         </is>
       </c>
     </row>
@@ -3805,7 +3839,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>193334</v>
+        <v>69044</v>
       </c>
     </row>
     <row r="5">
@@ -3815,7 +3849,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2595108</v>
+        <v>2664152</v>
       </c>
     </row>
     <row r="6">
@@ -3825,7 +3859,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20782346</v>
+        <v>20851390</v>
       </c>
     </row>
     <row r="7">
@@ -3835,7 +3869,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001986988694758479</v>
+        <v>0.0007095991778006167</v>
       </c>
     </row>
     <row r="8">
@@ -3845,7 +3879,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02667120246659815</v>
+        <v>0.02738080164439877</v>
       </c>
     </row>
     <row r="9">
@@ -3855,7 +3889,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2135904008221994</v>
+        <v>0.2143</v>
       </c>
     </row>
     <row r="10">
@@ -3865,7 +3899,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2076890.04109589</v>
+        <v>2049756.986486486</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$75</f>
+              <f>'DailyProfit'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$75</f>
+              <f>'DailyProfit'!$B$2:$B$76</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$75</f>
+              <f>'DailyProfit'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$75</f>
+              <f>'DailyProfit'!$D$2:$D$76</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$75</f>
+              <f>'DailyProfit'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$75</f>
+              <f>'DailyProfit'!$F$2:$F$76</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$75</f>
+              <f>'DailyProfit'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$75</f>
+              <f>'DailyProfit'!$G$2:$G$76</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$75</f>
+              <f>'DailyProfit'!$A$2:$A$76</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$75</f>
+              <f>'DailyProfit'!$H$2:$H$76</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3710,7 +3710,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
@@ -3741,6 +3741,40 @@
       </c>
       <c r="J75" s="11" t="n">
         <v>69044</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
+        <v>106839</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>2770991</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>20958229</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>9730</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>0.001098036998972251</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.02847883864337102</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>0.2153980369989723</v>
+      </c>
+      <c r="I76" s="11" t="n">
+        <v>37795</v>
+      </c>
+      <c r="J76" s="11" t="n">
+        <v>106839</v>
       </c>
     </row>
   </sheetData>
@@ -3818,7 +3852,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-26</t>
+          <t>2026-10-27</t>
         </is>
       </c>
     </row>
@@ -3839,7 +3873,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>69044</v>
+        <v>106839</v>
       </c>
     </row>
     <row r="5">
@@ -3849,7 +3883,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2664152</v>
+        <v>2770991</v>
       </c>
     </row>
     <row r="6">
@@ -3859,7 +3893,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20851390</v>
+        <v>20958229</v>
       </c>
     </row>
     <row r="7">
@@ -3869,7 +3903,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.0007095991778006167</v>
+        <v>0.001098036998972251</v>
       </c>
     </row>
     <row r="8">
@@ -3879,7 +3913,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02738080164439877</v>
+        <v>0.02847883864337102</v>
       </c>
     </row>
     <row r="9">
@@ -3889,7 +3923,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2143</v>
+        <v>0.2153980369989723</v>
       </c>
     </row>
     <row r="10">
@@ -3899,7 +3933,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2049756.986486486</v>
+        <v>2023851.413333333</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$76</f>
+              <f>'DailyProfit'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$76</f>
+              <f>'DailyProfit'!$B$2:$B$77</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$76</f>
+              <f>'DailyProfit'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$76</f>
+              <f>'DailyProfit'!$D$2:$D$77</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$76</f>
+              <f>'DailyProfit'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$76</f>
+              <f>'DailyProfit'!$F$2:$F$77</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$76</f>
+              <f>'DailyProfit'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$76</f>
+              <f>'DailyProfit'!$G$2:$G$77</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$76</f>
+              <f>'DailyProfit'!$A$2:$A$77</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$76</f>
+              <f>'DailyProfit'!$H$2:$H$77</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J76"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3744,7 +3744,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>2026-10-27</t>
         </is>
@@ -3775,6 +3775,40 @@
       </c>
       <c r="J76" s="11" t="n">
         <v>106839</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>118589284</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>55</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>29647321</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="I77" s="11" t="n">
+        <v>118482445</v>
+      </c>
+      <c r="J77" s="11" t="n">
+        <v>-20958174</v>
       </c>
     </row>
   </sheetData>
@@ -3852,7 +3886,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-10-28</t>
         </is>
       </c>
     </row>
@@ -3863,7 +3897,7 @@
         </is>
       </c>
       <c r="B3" s="11" t="n">
-        <v>9730</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -3873,7 +3907,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>106839</v>
+        <v>118589284</v>
       </c>
     </row>
     <row r="5">
@@ -3883,7 +3917,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>2770991</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6">
@@ -3893,7 +3927,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>20958229</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7">
@@ -3903,7 +3937,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.001098036998972251</v>
+        <v>29647321</v>
       </c>
     </row>
     <row r="8">
@@ -3913,7 +3947,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.02847883864337102</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="9">
@@ -3923,7 +3957,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.2153980369989723</v>
+        <v>13.75</v>
       </c>
     </row>
     <row r="10">
@@ -3933,7 +3967,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>2023851.413333333</v>
+        <v>3557607.105263158</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$77</f>
+              <f>'DailyProfit'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$77</f>
+              <f>'DailyProfit'!$B$2:$B$78</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$77</f>
+              <f>'DailyProfit'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$77</f>
+              <f>'DailyProfit'!$D$2:$D$78</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$77</f>
+              <f>'DailyProfit'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$77</f>
+              <f>'DailyProfit'!$F$2:$F$78</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$77</f>
+              <f>'DailyProfit'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$77</f>
+              <f>'DailyProfit'!$G$2:$G$78</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$77</f>
+              <f>'DailyProfit'!$A$2:$A$78</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$77</f>
+              <f>'DailyProfit'!$H$2:$H$78</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3778,7 +3778,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>2026-10-28</t>
         </is>
@@ -3809,6 +3809,40 @@
       </c>
       <c r="J77" s="11" t="n">
         <v>-20958174</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
+        <v>118830880</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>29707720</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I78" s="11" t="n">
+        <v>241596</v>
+      </c>
+      <c r="J78" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3886,7 +3920,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-28</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3941,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>118589284</v>
+        <v>118830880</v>
       </c>
     </row>
     <row r="5">
@@ -3917,7 +3951,7 @@
         </is>
       </c>
       <c r="B5" s="11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -3927,7 +3961,7 @@
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -3937,7 +3971,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>29647321</v>
+        <v>29707720</v>
       </c>
     </row>
     <row r="8">
@@ -3947,7 +3981,7 @@
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="9">
@@ -3957,7 +3991,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
@@ -3967,7 +4001,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>3557607.105263158</v>
+        <v>5054662.597402598</v>
       </c>
     </row>
     <row r="11">

--- a/samo.xlsx
+++ b/samo.xlsx
@@ -273,12 +273,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$78</f>
+              <f>'DailyProfit'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$B$2:$B$78</f>
+              <f>'DailyProfit'!$B$2:$B$79</f>
             </numRef>
           </val>
         </ser>
@@ -391,12 +391,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$78</f>
+              <f>'DailyProfit'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$D$2:$D$78</f>
+              <f>'DailyProfit'!$D$2:$D$79</f>
             </numRef>
           </val>
         </ser>
@@ -479,12 +479,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$78</f>
+              <f>'DailyProfit'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$F$2:$F$78</f>
+              <f>'DailyProfit'!$F$2:$F$79</f>
             </numRef>
           </val>
         </ser>
@@ -511,12 +511,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$78</f>
+              <f>'DailyProfit'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$G$2:$G$78</f>
+              <f>'DailyProfit'!$G$2:$G$79</f>
             </numRef>
           </val>
         </ser>
@@ -543,12 +543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'DailyProfit'!$A$2:$A$78</f>
+              <f>'DailyProfit'!$A$2:$A$79</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'DailyProfit'!$H$2:$H$78</f>
+              <f>'DailyProfit'!$H$2:$H$79</f>
             </numRef>
           </val>
         </ser>
@@ -1230,7 +1230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="14" bestFit="1" customWidth="1" style="3" min="1" max="1"/>
@@ -3812,7 +3812,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>2026-10-29</t>
         </is>
@@ -3843,6 +3843,40 @@
       </c>
       <c r="J78" s="11" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>118982761</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>29745690.25</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I79" s="11" t="n">
+        <v>151881</v>
+      </c>
+      <c r="J79" s="11" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3920,7 +3954,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29</t>
+          <t>2026-10-30</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3975,7 @@
         </is>
       </c>
       <c r="B4" s="11" t="n">
-        <v>118830880</v>
+        <v>118982761</v>
       </c>
     </row>
     <row r="5">
@@ -3971,7 +4005,7 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>29707720</v>
+        <v>29745690.25</v>
       </c>
     </row>
     <row r="8">
@@ -4001,7 +4035,7 @@
         </is>
       </c>
       <c r="B10" s="11" t="n">
-        <v>5054662.597402598</v>
+        <v>6515279.243589744</v>
       </c>
     </row>
     <row r="11">
